--- a/OUTPUT/gate_oof/fold_3/expert_inner_metrics.xlsx
+++ b/OUTPUT/gate_oof/fold_3/expert_inner_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,10 +535,10 @@
         <v>460</v>
       </c>
       <c r="H2" t="n">
-        <v>2.795118300000468</v>
+        <v>1.630447899980936</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03478809999978694</v>
+        <v>0.01889260002644733</v>
       </c>
       <c r="J2" t="n">
         <v>0.003791848606823045</v>
@@ -587,31 +587,31 @@
         <v>752</v>
       </c>
       <c r="H3" t="n">
-        <v>5.884091400001125</v>
+        <v>4.345767599996179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5200284000002284</v>
+        <v>0.5637378999963403</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005494903763766224</v>
+        <v>0.005500665106666104</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003986895700336168</v>
+        <v>0.003999725440119823</v>
       </c>
       <c r="L3" t="n">
-        <v>0.721613925296623</v>
+        <v>0.721029850114432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4156469331879993</v>
+        <v>0.4169764865439717</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.58263732190763e-05</v>
+        <v>-0.000100571709007015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01188479850463105</v>
+        <v>0.01180392643322219</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0180343819436507</v>
+        <v>0.01794531415414835</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         <v>1443</v>
       </c>
       <c r="H4" t="n">
-        <v>11.74596380000003</v>
+        <v>8.112386299995705</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6419652999993559</v>
+        <v>0.4718368999892846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005155314778835798</v>
+        <v>0.005155033478430138</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00389189132066839</v>
+        <v>0.003889221027431496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6380296688683538</v>
+        <v>0.6380691697048211</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3944994958062905</v>
+        <v>0.3942347876179368</v>
       </c>
       <c r="N4" t="n">
-        <v>2.161557317196604e-05</v>
+        <v>3.335388371791843e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01063025944968117</v>
+        <v>0.01062903366680728</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0214210667788749</v>
+        <v>0.02156838685571949</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +691,10 @@
         <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>2.777964400000201</v>
+        <v>1.836284100019839</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0363539000009041</v>
+        <v>0.01849479996599257</v>
       </c>
       <c r="J5" t="n">
         <v>0.003623842335767948</v>
@@ -743,31 +743,31 @@
         <v>752</v>
       </c>
       <c r="H6" t="n">
-        <v>7.635926299999483</v>
+        <v>4.320997299975716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5797740999987582</v>
+        <v>0.5688393000164069</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0058635041685795</v>
+        <v>0.005861825022970893</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004154651921984887</v>
+        <v>0.004146091632972822</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6791662003715918</v>
+        <v>0.6793499299339952</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4327347053825122</v>
+        <v>0.4318551071332258</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0003679651516647643</v>
+        <v>-0.0003487369200327883</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01270188555878635</v>
+        <v>0.01262148494966218</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02091132369919324</v>
+        <v>0.02141948449271769</v>
       </c>
     </row>
     <row r="7">
@@ -795,31 +795,31 @@
         <v>1443</v>
       </c>
       <c r="H7" t="n">
-        <v>15.18487360000108</v>
+        <v>9.411345400032587</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6688797000006161</v>
+        <v>0.4781354999868199</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005297915209791887</v>
+        <v>0.005303129374117302</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004062337671681709</v>
+        <v>0.004067753708132284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6064711412938282</v>
+        <v>0.6056961444136693</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4118397813071188</v>
+        <v>0.4123867941801095</v>
       </c>
       <c r="N7" t="n">
-        <v>5.287336568889841e-05</v>
+        <v>4.566236686445429e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0108756860492191</v>
+        <v>0.01082874176041539</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02095279929555816</v>
+        <v>0.02095753644662712</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +847,10 @@
         <v>460</v>
       </c>
       <c r="H8" t="n">
-        <v>4.433259800000087</v>
+        <v>1.888744299998507</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05031840000083321</v>
+        <v>0.01858850003918633</v>
       </c>
       <c r="J8" t="n">
         <v>0.003518943208870186</v>
@@ -899,31 +899,31 @@
         <v>752</v>
       </c>
       <c r="H9" t="n">
-        <v>9.937749299999268</v>
+        <v>4.43172809999669</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9684336999998777</v>
+        <v>0.611403800023254</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005415004703729218</v>
+        <v>0.005421097432413379</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003923997585437764</v>
+        <v>0.003926463241227343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7289876069223377</v>
+        <v>0.7283774010209163</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4088487012468929</v>
+        <v>0.4091005735689567</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0002817373270110396</v>
+        <v>-0.0002903347535942878</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01165566779508828</v>
+        <v>0.01168418058024329</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02118646332221064</v>
+        <v>0.02109679804364994</v>
       </c>
     </row>
     <row r="10">
@@ -951,31 +951,31 @@
         <v>1442</v>
       </c>
       <c r="H10" t="n">
-        <v>24.3418056999999</v>
+        <v>8.489049099967815</v>
       </c>
       <c r="I10" t="n">
-        <v>1.332114299999375</v>
+        <v>0.5586942000081763</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005473546861890301</v>
+        <v>0.005459191653339748</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004184003628576977</v>
+        <v>0.004162018942014987</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5928814241246679</v>
+        <v>0.5950140845230893</v>
       </c>
       <c r="M10" t="n">
-        <v>0.424319651719244</v>
+        <v>0.4220886198640409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001535991481653236</v>
+        <v>0.0001459066361033627</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01174141944010759</v>
+        <v>0.01185671094155115</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02067321955958257</v>
+        <v>0.02053143558563786</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>5.573824999999488</v>
+        <v>1.879338500031736</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0624759999991511</v>
+        <v>0.01807999995071441</v>
       </c>
       <c r="J11" t="n">
         <v>0.003507246919791521</v>
@@ -1055,31 +1055,31 @@
         <v>751</v>
       </c>
       <c r="H12" t="n">
-        <v>11.65593259999878</v>
+        <v>4.399668600002769</v>
       </c>
       <c r="I12" t="n">
-        <v>1.32439069999964</v>
+        <v>0.57702030002838</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005629028692653739</v>
+        <v>0.005616337208627874</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003952865206462368</v>
+        <v>0.003936296141226535</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7110558600184664</v>
+        <v>0.7123573264317622</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4115448978280876</v>
+        <v>0.409820157739339</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0004526815324266528</v>
+        <v>-0.0004462808043170934</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01213031509620988</v>
+        <v>0.01208860862228589</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02346702318505423</v>
+        <v>0.02345278904579895</v>
       </c>
     </row>
     <row r="13">
@@ -1107,31 +1107,31 @@
         <v>1442</v>
       </c>
       <c r="H13" t="n">
-        <v>23.68543470000077</v>
+        <v>8.066807699971832</v>
       </c>
       <c r="I13" t="n">
-        <v>1.059381299999586</v>
+        <v>0.4285106000024825</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005383815984646893</v>
+        <v>0.005392700045848002</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004040769848725589</v>
+        <v>0.004045756549604674</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6000729452439262</v>
+        <v>0.5987519833468271</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4096401075900182</v>
+        <v>0.4101543840282112</v>
       </c>
       <c r="N13" t="n">
-        <v>9.089945017703893e-05</v>
+        <v>9.602165564862207e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01118127683167039</v>
+        <v>0.0111869343152804</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02368361201745994</v>
+        <v>0.0240710522981612</v>
       </c>
     </row>
     <row r="14">
@@ -1159,10 +1159,10 @@
         <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>7.355971500001033</v>
+        <v>4.050521500001196</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06256140000004962</v>
+        <v>0.02334110002266243</v>
       </c>
       <c r="J14" t="n">
         <v>0.003845110241053771</v>
@@ -1211,31 +1211,31 @@
         <v>752</v>
       </c>
       <c r="H15" t="n">
-        <v>11.22522690000005</v>
+        <v>5.469237099983729</v>
       </c>
       <c r="I15" t="n">
-        <v>1.068100300000879</v>
+        <v>0.6780972999986261</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005502339996780598</v>
+        <v>0.005514842603986163</v>
       </c>
       <c r="K15" t="n">
-        <v>0.004049373276018376</v>
+        <v>0.004052669611960539</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7182665945328539</v>
+        <v>0.716984811157331</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4218191060962165</v>
+        <v>0.4221570938417881</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0002575894332983948</v>
+        <v>-0.0002562107685794362</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01154667951917746</v>
+        <v>0.01165041020089822</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02039733112839204</v>
+        <v>0.02036523123363854</v>
       </c>
     </row>
     <row r="16">
@@ -1263,31 +1263,31 @@
         <v>1442</v>
       </c>
       <c r="H16" t="n">
-        <v>21.92177999999876</v>
+        <v>166.2670603000442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9509052000012161</v>
+        <v>2.648009500000626</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005363608679350324</v>
+        <v>0.005365114061860259</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00410416107136558</v>
+        <v>0.004103470016525451</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6039246284643665</v>
+        <v>0.6037022674960664</v>
       </c>
       <c r="M16" t="n">
-        <v>0.416056245635221</v>
+        <v>0.4159853621273214</v>
       </c>
       <c r="N16" t="n">
-        <v>3.972459906585267e-05</v>
+        <v>3.584772922286665e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01088792007430771</v>
+        <v>0.0109029275153744</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02019292700359887</v>
+        <v>0.02034416846923659</v>
       </c>
     </row>
   </sheetData>
